--- a/data/trans_dic/IP1002-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen bornquitis crónica</t>
+          <t>Menores que padecen bornquitis crónica (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,98</t>
+          <t>0,51; 4,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,61</t>
+          <t>0,5; 4,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,11</t>
+          <t>0,53; 6,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,59</t>
+          <t>1,35; 6,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,49</t>
+          <t>0,0; 6,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,82</t>
+          <t>0,6; 2,73</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,56</t>
+          <t>1,23; 4,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,75</t>
+          <t>0,21; 1,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,5</t>
+          <t>0,64; 4,63</t>
         </is>
       </c>
     </row>
@@ -856,57 +857,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,92</t>
+          <t>0,64; 3,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,61</t>
+          <t>0,63; 4,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,27</t>
+          <t>0,52; 3,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,37</t>
+          <t>0,2; 2,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,49</t>
+          <t>0,31; 2,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,91</t>
+          <t>1,22; 4,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,05</t>
+          <t>0,89; 4,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,96</t>
+          <t>0,32; 3,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,55</t>
+          <t>0,65; 2,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,75</t>
+          <t>1,18; 3,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,9</t>
+          <t>0,9; 3,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,42</t>
+          <t>0,32; 3,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,28</t>
+          <t>0,73; 4,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,56</t>
+          <t>0,62; 4,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,9</t>
+          <t>1,19; 5,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,89</t>
+          <t>0,38; 3,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,63</t>
+          <t>0,72; 5,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,49</t>
+          <t>0,41; 2,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,15</t>
+          <t>1,39; 4,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,36</t>
+          <t>0,43; 2,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,14</t>
+          <t>0,97; 3,77</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,84</t>
+          <t>0,27; 2,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,22</t>
+          <t>0,35; 3,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,38</t>
+          <t>0,68; 4,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,14</t>
+          <t>0,32; 2,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,77</t>
+          <t>0,33; 3,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,57</t>
+          <t>0,56; 2,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,12</t>
+          <t>0,36; 2,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,3</t>
+          <t>0,52; 2,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,92</t>
+          <t>0,24; 1,75</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,2</t>
+          <t>0,73; 2,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,5</t>
+          <t>0,84; 2,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,84</t>
+          <t>0,57; 1,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,33</t>
+          <t>0,7; 2,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,12</t>
+          <t>0,61; 1,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,44</t>
+          <t>1,69; 3,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,23</t>
+          <t>0,8; 2,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,53</t>
+          <t>0,77; 2,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,83</t>
+          <t>0,85; 1,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,67</t>
+          <t>1,45; 2,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,77</t>
+          <t>0,84; 1,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,01</t>
+          <t>0,81; 1,99</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen bornquitis crónica (tasa de respuesta: 99,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2630</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2284</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2575</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2371</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3960</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7374</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4945</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>707; 6504</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>681; 6354</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4301</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>622; 7297</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4856</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2070; 10240</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3289</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 8987</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1747; 7979</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3575; 12742</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>578; 5023</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1649; 11891</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3570</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3385</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1536</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4689</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2532</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5596</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>9239</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7593</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4068</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1255; 7479</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1296; 8492</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1068; 6421</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>381; 4355</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>667; 5407</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2697; 10622</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1990; 8991</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>817; 7663</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2645; 9929</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5051; 15603</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3901; 13376</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1597; 9449</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1742</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3028</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3419</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4810</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4307</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7838</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3799</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>7726</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>446; 4674</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1131; 6684</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4471</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1174; 8569</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4236</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1975; 9734</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>636; 5791</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1341; 10958</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1168; 7496</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4459; 13598</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1391; 7988</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3650; 14141</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1641</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2386</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3791</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2133</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2148</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5432</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4213</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4534</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2614</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5977</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>565; 5922</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>717; 6421</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4071</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1406; 8944</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>666; 6120</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>683; 6331</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4431</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2340; 10972</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1498; 9010</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2128; 9769</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>835; 6108</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>9584</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10777</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7714</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8698</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>10656</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>18105</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>28664</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>17791</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>19354</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4955; 14993</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5958; 17024</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3992; 12658</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4649; 14870</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4393; 13975</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>12635; 27606</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5957; 16412</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5837; 18656</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>11998; 27440</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>21118; 38755</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>12131; 25866</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>11584; 28318</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1002-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,69</t>
+          <t>0,51; 4,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,66</t>
+          <t>0,49; 4,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,22</t>
+          <t>0,53; 7,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,69</t>
+          <t>1,38; 6,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,22</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,45</t>
+          <t>0,0; 6,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,73</t>
+          <t>0,48; 2,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,4</t>
+          <t>1,24; 4,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,78</t>
+          <t>0,21; 1,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,63</t>
+          <t>0,58; 4,32</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,83</t>
+          <t>0,65; 3,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,13</t>
+          <t>0,63; 3,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,1</t>
+          <t>0,34; 3,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,29</t>
+          <t>0,2; 2,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,55</t>
+          <t>0,31; 2,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,79</t>
+          <t>1,25; 4,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,01</t>
+          <t>0,91; 4,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,0</t>
+          <t>0,32; 3,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,44</t>
+          <t>0,73; 2,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,65</t>
+          <t>1,19; 3,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,1</t>
+          <t>0,96; 2,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,12</t>
+          <t>0,36; 1,98</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,39</t>
+          <t>0,32; 3,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,32</t>
+          <t>0,73; 4,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,52</t>
+          <t>0,54; 4,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,86</t>
+          <t>1,17; 5,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,47</t>
+          <t>0,41; 3,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,91</t>
+          <t>0,78; 6,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,61</t>
+          <t>0,41; 2,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,24</t>
+          <t>1,39; 4,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,48</t>
+          <t>0,45; 2,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,77</t>
+          <t>1,04; 4,14</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,82</t>
+          <t>0,27; 2,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,1</t>
+          <t>0,35; 3,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,3</t>
+          <t>0,68; 3,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,96</t>
+          <t>0,32; 2,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,08</t>
+          <t>0,33; 2,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,63</t>
+          <t>0,54; 2,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,16</t>
+          <t>0,39; 2,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,36</t>
+          <t>0,36; 2,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,75</t>
+          <t>0,17; 1,75</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,2</t>
+          <t>0,82; 2,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,41</t>
+          <t>0,91; 2,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,8</t>
+          <t>0,59; 1,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,23</t>
+          <t>0,76; 2,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,93</t>
+          <t>0,67; 2,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,69</t>
+          <t>1,55; 3,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,2</t>
+          <t>0,82; 2,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,45</t>
+          <t>0,75; 2,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,95</t>
+          <t>0,88; 1,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,66</t>
+          <t>1,41; 2,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,78</t>
+          <t>0,8; 1,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,99</t>
+          <t>0,91; 2,05</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>707; 6504</t>
+          <t>705; 6636</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>681; 6354</t>
+          <t>673; 6547</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4301</t>
+          <t>0; 4218</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>622; 7297</t>
+          <t>627; 8586</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4856</t>
+          <t>0; 4353</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2070; 10240</t>
+          <t>2112; 9543</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3289</t>
+          <t>0; 3331</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 8987</t>
+          <t>0; 9185</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1747; 7979</t>
+          <t>1409; 7742</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3575; 12742</t>
+          <t>3586; 13085</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>578; 5023</t>
+          <t>584; 5088</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1649; 11891</t>
+          <t>1493; 11085</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1255; 7479</t>
+          <t>1264; 7530</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1296; 8492</t>
+          <t>1295; 7507</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1068; 6421</t>
+          <t>696; 6255</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>381; 4355</t>
+          <t>380; 4876</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>667; 5407</t>
+          <t>666; 5040</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2697; 10622</t>
+          <t>2773; 10823</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1990; 8991</t>
+          <t>2036; 9681</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>817; 7663</t>
+          <t>822; 7693</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2645; 9929</t>
+          <t>2987; 10622</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5051; 15603</t>
+          <t>5078; 14975</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3901; 13376</t>
+          <t>4150; 12691</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1597; 9449</t>
+          <t>1620; 8839</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>446; 4674</t>
+          <t>445; 4860</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1131; 6684</t>
+          <t>1125; 7095</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4471</t>
+          <t>0; 4469</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1174; 8569</t>
+          <t>1016; 8037</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4236</t>
+          <t>0; 4751</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1975; 9734</t>
+          <t>1949; 9605</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>636; 5791</t>
+          <t>676; 6447</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1341; 10958</t>
+          <t>1448; 11163</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1168; 7496</t>
+          <t>1171; 6712</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4459; 13598</t>
+          <t>4453; 13583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1391; 7988</t>
+          <t>1458; 8647</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3650; 14141</t>
+          <t>3889; 15501</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5977</t>
+          <t>0; 5701</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>565; 5922</t>
+          <t>566; 6156</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>717; 6421</t>
+          <t>720; 6981</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4071</t>
+          <t>0; 4169</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1406; 8944</t>
+          <t>1411; 8266</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>666; 6120</t>
+          <t>667; 6149</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>683; 6331</t>
+          <t>689; 5758</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4431</t>
+          <t>0; 4777</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2340; 10972</t>
+          <t>2267; 10933</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1498; 9010</t>
+          <t>1634; 8571</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2128; 9769</t>
+          <t>1501; 9144</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>835; 6108</t>
+          <t>596; 6123</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4955; 14993</t>
+          <t>5571; 15385</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5958; 17024</t>
+          <t>6422; 17518</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3992; 12658</t>
+          <t>4151; 13589</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4649; 14870</t>
+          <t>5037; 15481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4393; 13975</t>
+          <t>4825; 14763</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12635; 27606</t>
+          <t>11606; 26197</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5957; 16412</t>
+          <t>6091; 16307</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5837; 18656</t>
+          <t>5675; 19366</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11998; 27440</t>
+          <t>12396; 25768</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21118; 38755</t>
+          <t>20506; 37721</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12131; 25866</t>
+          <t>11636; 25341</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11584; 28318</t>
+          <t>12932; 29264</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1002-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1002-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,78</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,8</t>
+          <t>1,41; 6,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 7,32</t>
+          <t>0,0; 5,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,51; 4,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,23</t>
+          <t>0,5; 4,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,59</t>
+          <t>0,52; 5,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,65</t>
+          <t>0,46; 2,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,52</t>
+          <t>1,25; 4,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,81</t>
+          <t>0,21; 1,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,32</t>
+          <t>0,62; 4,12</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,65%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,86</t>
+          <t>0,31; 2,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,65</t>
+          <t>1,24; 4,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,02</t>
+          <t>0,89; 4,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,56</t>
+          <t>0,36; 3,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,38</t>
+          <t>0,64; 3,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,88</t>
+          <t>0,64; 3,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,32</t>
+          <t>0,52; 3,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,02</t>
+          <t>0,18; 2,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,61</t>
+          <t>0,74; 2,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,5</t>
+          <t>1,18; 3,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,94</t>
+          <t>0,95; 2,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,98</t>
+          <t>0,41; 2,36</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,26%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,53</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,58</t>
+          <t>1,32; 5,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,38; 3,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,24</t>
+          <t>0,73; 6,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,33; 3,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,79</t>
+          <t>0,73; 4,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,87</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,02</t>
+          <t>0,79; 5,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,33</t>
+          <t>0,37; 2,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,23</t>
+          <t>1,39; 4,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,68</t>
+          <t>0,52; 2,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,14</t>
+          <t>1,07; 4,56</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,72</t>
+          <t>0,68; 4,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,93</t>
+          <t>0,32; 3,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,37</t>
+          <t>0,33; 2,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,98</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,97</t>
+          <t>0,27; 2,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,8</t>
+          <t>0,35; 3,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,62</t>
+          <t>0,55; 2,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,05</t>
+          <t>0,34; 2,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,21</t>
+          <t>0,52; 2,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,75</t>
+          <t>0,25; 1,84</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,26</t>
+          <t>0,58; 2,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,48</t>
+          <t>1,52; 3,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,93</t>
+          <t>0,81; 2,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,33</t>
+          <t>0,72; 2,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,04</t>
+          <t>0,76; 2,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,5</t>
+          <t>0,91; 2,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,19</t>
+          <t>0,54; 1,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,54</t>
+          <t>0,72; 2,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,84</t>
+          <t>0,86; 1,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,59</t>
+          <t>1,45; 2,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,75</t>
+          <t>0,85; 1,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,05</t>
+          <t>0,89; 2,05</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5090</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2630</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2284</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1213</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2575</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1329</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5090</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4330</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>705; 6636</t>
+          <t>0; 4736</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>673; 6547</t>
+          <t>2154; 10090</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4218</t>
+          <t>0; 3525</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>627; 8586</t>
+          <t>0; 6462</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4353</t>
+          <t>709; 6903</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2112; 9543</t>
+          <t>677; 6282</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3331</t>
+          <t>0; 3734</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 9185</t>
+          <t>626; 7257</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1409; 7742</t>
+          <t>1335; 8222</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3586; 13085</t>
+          <t>3607; 13215</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>584; 5088</t>
+          <t>579; 4938</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1493; 11085</t>
+          <t>1533; 10129</t>
         </is>
       </c>
     </row>
@@ -1717,37 +1717,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4689</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2684</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3570</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3385</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2904</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1536</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5854</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4689</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4237</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1264; 7530</t>
+          <t>665; 5282</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1295; 7507</t>
+          <t>2753; 10895</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>696; 6255</t>
+          <t>2005; 9084</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>380; 4876</t>
+          <t>853; 7974</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>666; 5040</t>
+          <t>1257; 7651</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2773; 10823</t>
+          <t>1319; 7419</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2036; 9681</t>
+          <t>1068; 6783</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>822; 7693</t>
+          <t>338; 4905</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2987; 10622</t>
+          <t>3009; 10400</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5078; 14975</t>
+          <t>5051; 16014</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4150; 12691</t>
+          <t>4102; 12522</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1620; 8839</t>
+          <t>1733; 9936</t>
         </is>
       </c>
     </row>
@@ -1925,37 +1925,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4810</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4109</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1742</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3028</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1211</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3419</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1375</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4810</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2588</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7577</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>445; 4860</t>
+          <t>0; 4894</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1125; 7095</t>
+          <t>2196; 9791</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4469</t>
+          <t>637; 6479</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1016; 8037</t>
+          <t>1225; 10513</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4751</t>
+          <t>448; 4709</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1949; 9605</t>
+          <t>1128; 6633</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>676; 6447</t>
+          <t>0; 4171</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1448; 11163</t>
+          <t>1232; 8291</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1171; 6712</t>
+          <t>1072; 7149</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4453; 13583</t>
+          <t>4465; 13311</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1458; 8647</t>
+          <t>1679; 7620</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3889; 15501</t>
+          <t>3488; 14806</t>
         </is>
       </c>
     </row>
@@ -2133,27 +2133,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3791</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2133</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2148</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1641</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2080</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2386</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1169</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3791</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2133</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2148</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2360</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5701</t>
+          <t>1413; 9108</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>566; 6156</t>
+          <t>668; 6504</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>720; 6981</t>
+          <t>682; 5707</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4169</t>
+          <t>0; 4538</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1411; 8266</t>
+          <t>0; 6429</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>667; 6149</t>
+          <t>566; 5976</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>689; 5758</t>
+          <t>724; 6688</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4777</t>
+          <t>0; 3231</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2267; 10933</t>
+          <t>2306; 10704</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1634; 8571</t>
+          <t>1406; 8832</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1501; 9144</t>
+          <t>2148; 9509</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>596; 6123</t>
+          <t>852; 6185</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>17887</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10077</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9876</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>9584</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>10777</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>7714</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8698</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>8521</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17887</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10077</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19354</t>
+          <t>18504</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5571; 15385</t>
+          <t>4177; 15357</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6422; 17518</t>
+          <t>11363; 25718</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4151; 13589</t>
+          <t>6040; 16584</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5037; 15481</t>
+          <t>5041; 17203</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4825; 14763</t>
+          <t>5199; 14993</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11606; 26197</t>
+          <t>6421; 17680</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6091; 16307</t>
+          <t>3827; 12962</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5675; 19366</t>
+          <t>4524; 15265</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12396; 25768</t>
+          <t>12002; 25622</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20506; 37721</t>
+          <t>21163; 38840</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11636; 25341</t>
+          <t>12253; 25723</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12932; 29264</t>
+          <t>11820; 27210</t>
         </is>
       </c>
     </row>
